--- a/analysis/tables/pythia-1.4b.xlsx
+++ b/analysis/tables/pythia-1.4b.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7944648142480932</v>
+        <v>0.5773110983536146</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1582232909751798</v>
+        <v>-0.07348037745538333</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.794x - 0.158</t>
+          <t>y = 0.577x - 0.073</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7987559504120979</v>
+        <v>0.7987559504120982</v>
       </c>
       <c r="H3" t="n">
         <v>0.07324930055186388</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1991570779946087</v>
+        <v>0.1272803825613883</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6362415232729135</v>
+        <v>0.5038307208982313</v>
       </c>
       <c r="K3" t="n">
         <v>0.1255702769574647</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8184070522412461</v>
+        <v>0.5758085218002534</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03588322026319704</v>
+        <v>-0.06800033294117808</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.818x - 0.036</t>
+          <t>y = 0.576x - 0.068</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8352175076561613</v>
+        <v>0.8025824809338078</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07202381469283513</v>
+        <v>0.07312068950510831</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04384519923787211</v>
+        <v>0.1180953917260141</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7825238319780491</v>
+        <v>0.5078081888590753</v>
       </c>
       <c r="K4" t="n">
         <v>0.1255702769574647</v>
